--- a/tools/setup-workbook/sample-candidates-batch2.xlsx
+++ b/tools/setup-workbook/sample-candidates-batch2.xlsx
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -557,11 +557,11 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Candidate 010</t>
+          <t>Umar Nguyen</t>
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="C2" s="6" t="n">
         <v>0.375</v>
@@ -570,11 +570,11 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Candidate 011</t>
+          <t>Vanessa Ong</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>0.3888888888888889</v>
@@ -583,11 +583,11 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Candidate 012</t>
+          <t>Wen Hui Tan</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>0.4027777777777778</v>
@@ -596,11 +596,11 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Candidate 013</t>
+          <t>Xavier Lee</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>0.4166666666666667</v>
@@ -609,11 +609,11 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Candidate 014</t>
+          <t>Yasmin Wijaya</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>0.4305555555555556</v>
@@ -622,11 +622,11 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Candidate 015</t>
+          <t>Zhi Hao Lim</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>0.4513888888888889</v>
@@ -635,14 +635,950 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Candidate 001</t>
+          <t>Aisha Chen</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>0.4652777777777778</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Benjamin Hassan</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0.4791666666666667</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Chloe Ng</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>0.4930555555555556</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Daniel Ismail</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Elena Chua</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Farid Kumar</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0.4027777777777778</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Grace Goh</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Hafiz Reyes</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>0.4305555555555556</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Ivy Wong</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>0.4513888888888889</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Jun Wei Pillai</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>0.4652777777777778</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Kavya Koh</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>0.4791666666666667</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Liam Nguyen</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0.4930555555555556</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Mei Ling Ong</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Nathan Tan</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>0.5972222222222222</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Olivia Lee</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Priya Wijaya</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Qistina Lim</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>0.6388888888888888</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Rahul Santoso</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Sarah Teo</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Thanh Rahman</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>0.4027777777777778</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Umar Chen</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Vanessa Hassan</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>0.4305555555555556</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Wen Hui Ng</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>0.4513888888888889</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Xavier Ismail</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>0.4652777777777778</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Yasmin Chua</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>0.4791666666666667</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Zhi Hao Kumar</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>0.4930555555555556</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Aisha Pillai</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Benjamin Koh</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>0.5972222222222222</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Chloe Nguyen</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Daniel Ong</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Elena Tan</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>0.6388888888888888</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Farid Lee</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>0.6597222222222222</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Grace Wijaya</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>0.6736111111111112</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Hafiz Lim</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Ivy Santoso</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>0.7013888888888888</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Jun Wei Teo</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Kavya Rahman</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Liam Chen</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>0.4027777777777778</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Mei Ling Hassan</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Nathan Ng</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>0.4305555555555556</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Olivia Ismail</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>0.4513888888888889</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Priya Chua</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>0.4652777777777778</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Qistina Kumar</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>0.4791666666666667</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Rahul Goh</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>0.4930555555555556</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Sarah Reyes</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Thanh Wong</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>0.5972222222222222</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Umar Pillai</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Vanessa Koh</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Wen Hui Nguyen</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>0.6388888888888888</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Xavier Ong</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>0.6597222222222222</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Yasmin Tan</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>0.6736111111111112</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Zhi Hao Lee</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Aisha Teo</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>0.7013888888888888</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Benjamin Rahman</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Chloe Chen</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Daniel Hassan</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>0.4027777777777778</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Elena Ng</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Farid Ismail</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>0.4305555555555556</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Grace Chua</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>0.4513888888888889</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Hafiz Kumar</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C67" s="6" t="n">
+        <v>0.4652777777777778</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Ivy Goh</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>0.4791666666666667</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>Jun Wei Reyes</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C69" s="6" t="n">
+        <v>0.4930555555555556</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Kavya Wong</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>Liam Pillai</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C71" s="6" t="n">
+        <v>0.5972222222222222</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Mei Ling Koh</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>Nathan Nguyen</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C73" s="6" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Olivia Ong</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C74" s="6" t="n">
+        <v>0.6388888888888888</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>Priya Tan</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C75" s="6" t="n">
+        <v>0.6597222222222222</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Aisha Tan</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>Benjamin Lee</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C77" s="6" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Chloe Wijaya</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>0.6736111111111112</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Daniel Lim</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C79" s="6" t="n">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Elena Santoso</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C80" s="6" t="n">
+        <v>0.7013888888888888</v>
       </c>
     </row>
   </sheetData>
